--- a/moduli/3-alzatina/alzatina_costi.xlsx
+++ b/moduli/3-alzatina/alzatina_costi.xlsx
@@ -20,18 +20,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="61">
   <si>
     <t xml:space="preserve">Modulo 3 – Alzatina con mensola: distinta e costi</t>
   </si>
   <si>
-    <t xml:space="preserve">Si monta sul tavolo base usando le predisposizioni (fori e dadi nelle gambe posteriori). Celle gialle = stime.</t>
+    <t xml:space="preserve">Si monta sul tavolo base usando le predisposizioni. Prezzi verificati il 18/10/2026; celle gialle = stime.</t>
   </si>
   <si>
     <t xml:space="preserve">Categoria</t>
   </si>
   <si>
-    <t xml:space="preserve">Articolo</t>
+    <t xml:space="preserve">Articolo (prodotto trovato)</t>
   </si>
   <si>
     <t xml:space="preserve">Uso</t>
@@ -52,13 +52,22 @@
     <t xml:space="preserve">Fonte prezzo</t>
   </si>
   <si>
+    <t xml:space="preserve">Negozio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
     <t xml:space="preserve">Legno</t>
   </si>
   <si>
     <t xml:space="preserve">Montanti KVH 80×120×250</t>
   </si>
   <si>
-    <t xml:space="preserve">tagliati con le travi del tavolo base (barre 3 e 4)</t>
+    <t xml:space="preserve">tagliati con le travi del tavolo base</t>
   </si>
   <si>
     <t xml:space="preserve">pz</t>
@@ -67,64 +76,100 @@
     <t xml:space="preserve">incluso nel tavolo base</t>
   </si>
   <si>
-    <t xml:space="preserve">Tavola lamellare abete OBI 800×200×14</t>
+    <t xml:space="preserve">Tecnomat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tavola in abete lamellare 1000×200×18</t>
   </si>
   <si>
     <t xml:space="preserve">mensola: tagliate a 620, 780 e 600</t>
   </si>
   <si>
-    <t xml:space="preserve">OBI, verificato 18/10/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Listello abete 30×40, barra 2,4 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rinforzo sotto il bordo anteriore (2000)</t>
+    <t xml:space="preserve">verificato 18/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">apri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OBI 800×200×18 8,79 €; OBI 800×200×14 8,19 €</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Listello abete grezzo 30×40×2000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rinforzo sotto il bordo anteriore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visibile dal basso: levigalo. Piallato 30×40×2000 da OBI a 3,99 €</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ferramenta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barra filettata M10×1000 zincata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 spezzoni da 390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dado cieco M10 + rondella Ø30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sopra la mensola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">set</t>
   </si>
   <si>
     <t xml:space="preserve">stima – da verificare</t>
   </si>
   <si>
-    <t xml:space="preserve">Ferramenta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barra filettata M10 da 1 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 spezzoni da 380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dado cieco M10 + rondella Ø30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sopra la mensola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">set</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dadi a tamburo M10 nelle gambe posteriori</t>
   </si>
   <si>
     <t xml:space="preserve">già montati con il tavolo base</t>
   </si>
   <si>
-    <t xml:space="preserve">Viti 4×50 (conf.) + colla</t>
+    <t xml:space="preserve">ferramenta/online</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viti 4×50</t>
   </si>
   <si>
     <t xml:space="preserve">listello sotto le tavole</t>
   </si>
   <si>
-    <t xml:space="preserve">Angolare a L 100×100 + tassello Ø8</t>
+    <t xml:space="preserve">conf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collante vinilico D3 Tover 500 ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">listello</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se avanza dal tavolo base: 0 €</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staffa angolare con nervatura 90×90×65 zincata</t>
   </si>
   <si>
     <t xml:space="preserve">fissaggio a muro su M1 e M4</t>
   </si>
   <si>
+    <t xml:space="preserve">OBI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tasselli Ø8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fissaggio a muro</t>
+  </si>
+  <si>
     <t xml:space="preserve">Finitura</t>
   </si>
   <si>
-    <t xml:space="preserve">Olio/impregnante (quota)</t>
+    <t xml:space="preserve">Impregnante (quota)</t>
   </si>
   <si>
     <t xml:space="preserve">mensola e montanti</t>
@@ -148,10 +193,16 @@
     <t xml:space="preserve">di cui finitura</t>
   </si>
   <si>
-    <t xml:space="preserve">Se il tavolo base è già montato senza i 4 montanti, servono 1 m di KVH 80×120: una barra da 4 m costa 29,90 €.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tavole OBI: prezzo verificato il 18/10/2026 (articolo 2423135).</t>
+    <t xml:space="preserve">da OBI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">da Tecnomat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">da ferramenta/online</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se il tavolo base è già montato senza i montanti, serve 1 m di KVH 80×120: una barra da 4 m costa 29,90 € (Tecnomat).</t>
   </si>
 </sst>
 </file>
@@ -163,7 +214,7 @@
     <numFmt numFmtId="165" formatCode="0"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot; €&quot;;\-#,##0.00&quot; €&quot;;\-"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -221,6 +272,14 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <u val="single"/>
+      <sz val="11"/>
+      <color rgb="FF1F5FA8"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -291,7 +350,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -325,6 +384,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -377,7 +440,7 @@
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FF1F5FA8"/>
       <rgbColor rgb="FFCCCCFF"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
@@ -596,16 +659,19 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="46"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -643,22 +709,31 @@
       <c r="H4" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>0</v>
@@ -668,107 +743,137 @@
         <v>0</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>17</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="4"/>
+      <c r="K5" s="5"/>
+    </row>
+    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>3</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>8.19</v>
+        <v>4.5</v>
       </c>
       <c r="G6" s="8" t="n">
         <f aca="false">D6*F6</f>
-        <v>24.57</v>
+        <v>13.5</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>21</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>5</v>
+        <v>16</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>3.1</v>
       </c>
       <c r="G7" s="8" t="n">
         <f aca="false">D7*F7</f>
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>21</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>3.5</v>
+        <v>16</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>1.65</v>
       </c>
       <c r="G8" s="8" t="n">
         <f aca="false">D8*F8</f>
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>21</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" s="5"/>
+    </row>
+    <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="F9" s="10" t="n">
         <v>0.8</v>
       </c>
       <c r="G9" s="8" t="n">
@@ -776,24 +881,29 @@
         <v>3.2</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>33</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="4"/>
+      <c r="K9" s="5"/>
+    </row>
+    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F10" s="7" t="n">
         <v>0</v>
@@ -803,155 +913,274 @@
         <v>0</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>17</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J10" s="4"/>
+      <c r="K10" s="5"/>
+    </row>
+    <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>6</v>
+        <v>39</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="G11" s="8" t="n">
         <f aca="false">D11*F11</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>33</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" s="4"/>
+      <c r="K11" s="5"/>
+    </row>
+    <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>4</v>
+        <v>16</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>4.95</v>
       </c>
       <c r="G12" s="8" t="n">
         <f aca="false">D12*F12</f>
-        <v>8</v>
+        <v>4.95</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>21</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>8</v>
+        <v>16</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>2.89</v>
       </c>
       <c r="G13" s="8" t="n">
         <f aca="false">D13*F13</f>
-        <v>8</v>
+        <v>5.78</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F15" s="10" t="s">
-        <v>36</v>
+        <v>21</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="5"/>
+    </row>
+    <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <f aca="false">D14*F14</f>
+        <v>2</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" s="4"/>
+      <c r="K14" s="5"/>
+    </row>
+    <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="G15" s="8" t="n">
-        <f aca="false">SUMIFS(G5:G13,H5:H13,"fornito da te")+SUMIFS(G5:G13,H5:H13,"OBI, verificato 18/10/2026")</f>
-        <v>24.57</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F16" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="G16" s="8" t="n">
-        <f aca="false">SUMIFS(G5:G13,H5:H13,"stima – da verificare")</f>
-        <v>37.2</v>
-      </c>
+        <f aca="false">D15*F15</f>
+        <v>3</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" s="4"/>
+      <c r="K15" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F17" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="G17" s="12" t="n">
-        <f aca="false">SUM(G5:G13)</f>
-        <v>61.77</v>
+        <v>51</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <f aca="false">SUMIFS(G5:G15,H5:H15,"verificato 18/10/2026")</f>
+        <v>30.63</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F18" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <f aca="false">SUMIFS(G5:G15,H5:H15,"stima – da verificare")</f>
+        <v>11.2</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F19" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="G19" s="8" t="n">
-        <f aca="false">SUMIFS(G5:G13,A5:A13,"Legno")</f>
-        <v>29.57</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F20" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="G20" s="8" t="n">
-        <f aca="false">SUMIFS(G5:G13,A5:A13,"Ferramenta")</f>
-        <v>24.2</v>
+      <c r="F19" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" s="13" t="n">
+        <f aca="false">SUM(G5:G15)</f>
+        <v>41.83</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F21" s="10" t="s">
-        <v>41</v>
+      <c r="F21" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="G21" s="8" t="n">
-        <f aca="false">SUMIFS(G5:G13,A5:A13,"Finitura")</f>
-        <v>8</v>
+        <f aca="false">SUMIFS(G5:G15,A5:A15,"Legno")</f>
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F22" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G22" s="8" t="n">
+        <f aca="false">SUMIFS(G5:G15,A5:A15,"Ferramenta")</f>
+        <v>22.23</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
-        <v>43</v>
+      <c r="F23" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="G23" s="8" t="n">
+        <f aca="false">SUMIFS(G5:G15,A5:A15,"Finitura")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F25" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G25" s="8" t="n">
+        <f aca="false">SUMIFS(G5:G15,I5:I15,"OBI")</f>
+        <v>5.78</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F26" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G26" s="8" t="n">
+        <f aca="false">SUMIFS(G5:G15,I5:I15,"Tecnomat")</f>
+        <v>36.05</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F27" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G27" s="8" t="n">
+        <f aca="false">SUMIFS(G5:G15,I5:I15,"ferramenta/online")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="J6" r:id="rId1" display="apri"/>
+    <hyperlink ref="J7" r:id="rId2" display="apri"/>
+    <hyperlink ref="J8" r:id="rId3" display="apri"/>
+    <hyperlink ref="J12" r:id="rId4" display="apri"/>
+    <hyperlink ref="J13" r:id="rId5" display="apri"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/moduli/3-alzatina/alzatina_costi.xlsx
+++ b/moduli/3-alzatina/alzatina_costi.xlsx
@@ -97,7 +97,7 @@
     <t xml:space="preserve">Listello abete grezzo 30×40×2000</t>
   </si>
   <si>
-    <t xml:space="preserve">rinforzo sotto il bordo anteriore</t>
+    <t xml:space="preserve">rinforzo sotto il bordo anteriore: 3 pezzi tra i montanti (500, 700, 480)</t>
   </si>
   <si>
     <t xml:space="preserve">Visibile dal basso: levigalo. Piallato 30×40×2000 da OBI a 3,99 €</t>
@@ -154,7 +154,7 @@
     <t xml:space="preserve">Staffa angolare con nervatura 90×90×65 zincata</t>
   </si>
   <si>
-    <t xml:space="preserve">fissaggio a muro su M1 e M4</t>
+    <t xml:space="preserve">fissaggio a muro sotto la mensola, vicino a M1 e M4</t>
   </si>
   <si>
     <t xml:space="preserve">OBI</t>
